--- a/bin/attorney.xlsx
+++ b/bin/attorney.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prg\GGRM\bin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F2">
         <f ca="1">RAND()*2</f>
-        <v>1.4338493701958159</v>
+        <v>1.0456139633043453</v>
       </c>
       <c r="G2" t="s">
         <v>54</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F26" ca="1" si="1">RAND()*2</f>
-        <v>1.2679254295231361</v>
+        <v>1.968997676408593</v>
       </c>
       <c r="G3" t="s">
         <v>55</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F4">
         <f t="shared" ca="1" si="1"/>
-        <v>9.8504920790331907E-2</v>
+        <v>0.93618199605370811</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1124,15 +1124,15 @@
       </c>
       <c r="E5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
+        <v>Workers Compensation</v>
       </c>
       <c r="F5">
         <f t="shared" ca="1" si="1"/>
-        <v>1.403303446511897</v>
+        <v>0.21256059758441026</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1568, 'Brock', 'Allison', 'Personal Injury'),</v>
+        <v>(1568, 'Brock', 'Allison', 'Workers Compensation'),</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F6">
         <f t="shared" ca="1" si="1"/>
-        <v>1.6947605994719133</v>
+        <v>1.5924004048466511</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="F7">
         <f t="shared" ca="1" si="1"/>
-        <v>0.17654953099514548</v>
+        <v>0.6656590920043941</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F8">
         <f t="shared" ca="1" si="1"/>
-        <v>0.31170014716951577</v>
+        <v>0.41424533441045219</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F9">
         <f t="shared" ca="1" si="1"/>
-        <v>1.8922096844098928</v>
+        <v>1.0576334377503178</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1254,15 +1254,15 @@
       </c>
       <c r="E10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
+        <v>Personal Injury</v>
       </c>
       <c r="F10">
         <f t="shared" ca="1" si="1"/>
-        <v>2.4972950617948797E-2</v>
+        <v>1.8988623747771594</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(664, 'Rhoda', 'Bean', 'Workers Compensation'),</v>
+        <v>(664, 'Rhoda', 'Bean', 'Personal Injury'),</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F11">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73556934220455195</v>
+        <v>0.82908201825825945</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F12">
         <f t="shared" ca="1" si="1"/>
-        <v>0.61603923870009925</v>
+        <v>0.23170021598962598</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1332,15 +1332,15 @@
       </c>
       <c r="E13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
+        <v>Workers Compensation</v>
       </c>
       <c r="F13">
         <f t="shared" ca="1" si="1"/>
-        <v>1.1106950103530826</v>
+        <v>0.58418822890033084</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1727, 'Whoopi', 'Campos', 'Personal Injury'),</v>
+        <v>(1727, 'Whoopi', 'Campos', 'Workers Compensation'),</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1358,15 +1358,15 @@
       </c>
       <c r="E14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
+        <v>Personal Injury</v>
       </c>
       <c r="F14">
         <f t="shared" ca="1" si="1"/>
-        <v>0.25933547005608371</v>
+        <v>1.7511233737801835</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(901, 'Lila', 'Bond', 'Workers Compensation'),</v>
+        <v>(901, 'Lila', 'Bond', 'Personal Injury'),</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1384,15 +1384,15 @@
       </c>
       <c r="E15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
+        <v>Workers Compensation</v>
       </c>
       <c r="F15">
         <f t="shared" ca="1" si="1"/>
-        <v>1.7803410600149749</v>
+        <v>0.84178681885030993</v>
       </c>
       <c r="H15" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1049, 'Kibo', 'Rowe', 'Personal Injury'),</v>
+        <v>(1049, 'Kibo', 'Rowe', 'Workers Compensation'),</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1410,15 +1410,15 @@
       </c>
       <c r="E16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
+        <v>Personal Injury</v>
       </c>
       <c r="F16">
         <f t="shared" ca="1" si="1"/>
-        <v>0.42669772700024144</v>
+        <v>1.573967708896953</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1342, 'Tanner', 'Freeman', 'Workers Compensation'),</v>
+        <v>(1342, 'Tanner', 'Freeman', 'Personal Injury'),</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F17">
         <f t="shared" ca="1" si="1"/>
-        <v>1.9934460123114357</v>
+        <v>1.7073722331035723</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1462,15 +1462,15 @@
       </c>
       <c r="E18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
+        <v>Personal Injury</v>
       </c>
       <c r="F18">
         <f t="shared" ca="1" si="1"/>
-        <v>0.63721968852543198</v>
+        <v>1.6419827392027313</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1859, 'Matthew', 'Murphy', 'Workers Compensation'),</v>
+        <v>(1859, 'Matthew', 'Murphy', 'Personal Injury'),</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F19">
         <f t="shared" ca="1" si="1"/>
-        <v>0.26018284381300449</v>
+        <v>0.19268020366984384</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1514,15 +1514,15 @@
       </c>
       <c r="E20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
+        <v>Workers Compensation</v>
       </c>
       <c r="F20">
         <f t="shared" ca="1" si="1"/>
-        <v>1.0023830909162228</v>
+        <v>0.55275792177304295</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(753, 'Helen', 'Gordon', 'Personal Injury'),</v>
+        <v>(753, 'Helen', 'Gordon', 'Workers Compensation'),</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1540,15 +1540,15 @@
       </c>
       <c r="E21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Personal Injury</v>
+        <v>Workers Compensation</v>
       </c>
       <c r="F21">
         <f t="shared" ca="1" si="1"/>
-        <v>1.2142102671131663</v>
+        <v>0.38937428654879591</v>
       </c>
       <c r="H21" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(1238, 'Lee', 'Justice', 'Personal Injury'),</v>
+        <v>(1238, 'Lee', 'Justice', 'Workers Compensation'),</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1566,15 +1566,15 @@
       </c>
       <c r="E22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
+        <v>Personal Injury</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84297726302142673</v>
+        <v>1.1275589904946437</v>
       </c>
       <c r="H22" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(249, 'Karleigh', 'Flowers', 'Workers Compensation'),</v>
+        <v>(249, 'Karleigh', 'Flowers', 'Personal Injury'),</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="1"/>
-        <v>1.59842343040693</v>
+        <v>1.3865112512367832</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="1"/>
-        <v>0.63318042793500173</v>
+        <v>0.11313850166678141</v>
       </c>
       <c r="H24" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="1"/>
-        <v>0.15218490045927213</v>
+        <v>0.39632713261647967</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1670,15 +1670,15 @@
       </c>
       <c r="E26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Workers Compensation</v>
+        <v>Personal Injury</v>
       </c>
       <c r="F26">
         <f t="shared" ca="1" si="1"/>
-        <v>0.38863038219256962</v>
+        <v>1.3014419047896062</v>
       </c>
       <c r="H26" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>(14, 'Latifah', 'Nolan', 'Workers Compensation'),</v>
+        <v>(14, 'Latifah', 'Nolan', 'Personal Injury'),</v>
       </c>
     </row>
   </sheetData>
